--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104475_W2.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104475_W2.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.2833</v>
+        <v>4.879</v>
       </c>
       <c r="E2" t="n">
-        <v>1.9223</v>
+        <v>2.4856</v>
       </c>
       <c r="F2" t="n">
-        <v>2.361</v>
+        <v>2.3935</v>
       </c>
       <c r="G2" t="n">
-        <v>3.3147</v>
+        <v>3.3226</v>
       </c>
       <c r="H2" t="n">
-        <v>2.1499</v>
+        <v>2.1593</v>
       </c>
       <c r="I2" t="n">
-        <v>1.1648</v>
+        <v>1.1633</v>
       </c>
       <c r="J2" t="n">
-        <v>1.6877</v>
+        <v>1.6705</v>
       </c>
       <c r="K2" t="n">
-        <v>1.5066</v>
+        <v>1.4996</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1812</v>
+        <v>0.1708</v>
       </c>
       <c r="M2" t="n">
-        <v>1.6269</v>
+        <v>1.6522</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6433</v>
+        <v>0.6597</v>
       </c>
       <c r="O2" t="n">
-        <v>0.9837</v>
+        <v>0.9925</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5777</v>
+        <v>0.0117</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5898</v>
+        <v>0.0019</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0121</v>
+        <v>0.0097</v>
       </c>
       <c r="V2" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W2" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="3">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.2738</v>
+        <v>4.1172</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4507</v>
+        <v>2.3907</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8231</v>
+        <v>1.7264</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6731</v>
+        <v>2.6819</v>
       </c>
       <c r="H3" t="n">
-        <v>2.2279</v>
+        <v>2.2287</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4452</v>
+        <v>0.4532</v>
       </c>
       <c r="J3" t="n">
-        <v>2.6775</v>
+        <v>2.6655</v>
       </c>
       <c r="K3" t="n">
-        <v>2.5282</v>
+        <v>2.5166</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1493</v>
+        <v>0.1489</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0044</v>
+        <v>0.0164</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3003</v>
+        <v>-0.2879</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2959</v>
+        <v>0.3043</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9448</v>
+        <v>0.7736</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5444</v>
+        <v>0.4991</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4004</v>
+        <v>0.2744</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. KRAMPELJ</t>
+          <t>M. PANTZAR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7163</v>
+        <v>2.5841</v>
       </c>
       <c r="E4" t="n">
-        <v>0.961</v>
+        <v>0.8699</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7553</v>
+        <v>1.7142</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7704</v>
+        <v>3.5183</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6796</v>
+        <v>1.7978</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4501</v>
+        <v>1.7206</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0126</v>
+        <v>2.8266</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.3952</v>
+        <v>1.9855</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4078</v>
+        <v>0.8411</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7578</v>
+        <v>0.6917</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2844</v>
+        <v>-0.1877</v>
       </c>
       <c r="O4" t="n">
-        <v>1.0423</v>
+        <v>0.8794999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.9073</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.2683</v>
+        <v>-3.6421</v>
       </c>
       <c r="R4" t="n">
-        <v>1.361</v>
+        <v>1.5934</v>
       </c>
       <c r="S4" t="n">
-        <v>1.7605</v>
+        <v>-0.0613</v>
       </c>
       <c r="T4" t="n">
-        <v>1.8026</v>
+        <v>-0.0351</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0421</v>
+        <v>-0.0262</v>
       </c>
       <c r="V4" t="n">
-        <v>1.0927</v>
+        <v>1.1758</v>
       </c>
       <c r="W4" t="n">
-        <v>1.4141</v>
+        <v>1.7205</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.3214</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. PANTZAR</t>
+          <t>L. PETRASEK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7725</v>
+        <v>1.8821</v>
       </c>
       <c r="E5" t="n">
-        <v>0.126</v>
+        <v>-2.0135</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6465</v>
+        <v>3.8955</v>
       </c>
       <c r="G5" t="n">
-        <v>3.5143</v>
+        <v>0.6578000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>1.795</v>
+        <v>0.2469</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7193</v>
+        <v>0.4109</v>
       </c>
       <c r="J5" t="n">
-        <v>2.8545</v>
+        <v>-0.7959000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>2.0016</v>
+        <v>-0.5417999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8529</v>
+        <v>-0.2541</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6598000000000001</v>
+        <v>1.4537</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2066</v>
+        <v>0.7887</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8663999999999999</v>
+        <v>0.665</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.0415</v>
+        <v>0.2276</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.6293</v>
+        <v>-2.2763</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5878</v>
+        <v>2.5039</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8895</v>
+        <v>-0.0929</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8347</v>
+        <v>-0.0307</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0548</v>
+        <v>-0.0621</v>
       </c>
       <c r="V5" t="n">
-        <v>1.1892</v>
+        <v>1.0895</v>
       </c>
       <c r="W5" t="n">
-        <v>1.7355</v>
+        <v>1.0895</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5463</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. PETRASEK</t>
+          <t>J. JAWORSKI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3182</v>
+        <v>1.7233</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.2242</v>
+        <v>1.5532</v>
       </c>
       <c r="F6" t="n">
-        <v>3.5424</v>
+        <v>0.1701</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6611</v>
+        <v>0.06</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2453</v>
+        <v>-0.2469</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4158</v>
+        <v>0.3069</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.7582</v>
+        <v>0.0725</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5235</v>
+        <v>0.3857</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.2347</v>
+        <v>-0.3132</v>
       </c>
       <c r="M6" t="n">
-        <v>1.4193</v>
+        <v>-0.0125</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7688</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6505</v>
+        <v>0.6201</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>2.4952</v>
+        <v>1.3658</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6623</v>
+        <v>-0.1985</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2903</v>
+        <v>-0.1048</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.372</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0927</v>
+        <v>1.6342</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0927</v>
+        <v>2.7237</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. JAWORSKI</t>
+          <t>M. KRAMPELJ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7817</v>
+        <v>1.6403</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8602</v>
+        <v>-0.1103</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0785</v>
+        <v>1.7506</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0613</v>
+        <v>0.7703</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2453</v>
+        <v>-0.6806</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3065</v>
+        <v>1.4509</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0974</v>
+        <v>-0.0052</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4014</v>
+        <v>-0.4072</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.3039</v>
+        <v>0.4019</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0362</v>
+        <v>0.7755</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.2734</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6105</v>
+        <v>1.049</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2268</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R7" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1454</v>
+        <v>0.6911</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8347</v>
+        <v>0.7662</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3106</v>
+        <v>-0.0752</v>
       </c>
       <c r="V7" t="n">
-        <v>1.639</v>
+        <v>1.0895</v>
       </c>
       <c r="W7" t="n">
-        <v>2.7317</v>
+        <v>1.405</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0927</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7029</v>
+        <v>0.5424</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6919</v>
+        <v>-0.755</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3948</v>
+        <v>1.2974</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2007</v>
+        <v>-0.1929</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8298</v>
+        <v>-0.8246</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6291</v>
+        <v>0.6317</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.695</v>
+        <v>-0.7106</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6549</v>
+        <v>-0.6657</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.04</v>
+        <v>-0.0449</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4943</v>
+        <v>0.5178</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1749</v>
+        <v>-0.1588</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6691</v>
+        <v>0.6766</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5426</v>
+        <v>0.3695</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2299</v>
+        <v>0.1833</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3127</v>
+        <v>0.1862</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="9">
@@ -1111,22 +1111,22 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0231</v>
+        <v>0.2445</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1391</v>
+        <v>0.0487</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1622</v>
+        <v>0.1958</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1414</v>
+        <v>0.1435</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0159</v>
+        <v>-0.0144</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1138,13 +1138,13 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1414</v>
+        <v>0.1435</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0159</v>
+        <v>-0.0144</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1183</v>
+        <v>0.101</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1391</v>
+        <v>0.0487</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0209</v>
+        <v>0.0523</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5021</v>
+        <v>0.1318</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6823</v>
+        <v>-2.2446</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1802</v>
+        <v>2.3764</v>
       </c>
       <c r="G10" t="n">
-        <v>1.0473</v>
+        <v>1.0495</v>
       </c>
       <c r="H10" t="n">
-        <v>2.9478</v>
+        <v>2.955</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.9006</v>
+        <v>-1.9054</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1906</v>
+        <v>-0.2158</v>
       </c>
       <c r="K10" t="n">
-        <v>2.3204</v>
+        <v>2.3097</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.511</v>
+        <v>-2.5255</v>
       </c>
       <c r="M10" t="n">
-        <v>1.2379</v>
+        <v>1.2653</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6274</v>
+        <v>0.6452</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6105</v>
+        <v>0.6201</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R10" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7516</v>
+        <v>-0.1242</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5202</v>
+        <v>-0.0468</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2314</v>
+        <v>-0.0774</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.4783</v>
+        <v>-1.4764</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.6105</v>
+        <v>-0.6162</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.8678</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.1503</v>
+        <v>-1.5564</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3717</v>
+        <v>0.4253</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.522</v>
+        <v>-1.9817</v>
       </c>
       <c r="G11" t="n">
-        <v>2.4526</v>
+        <v>2.4719</v>
       </c>
       <c r="H11" t="n">
-        <v>1.7675</v>
+        <v>1.7773</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6851</v>
+        <v>0.6946</v>
       </c>
       <c r="J11" t="n">
-        <v>1.5292</v>
+        <v>1.5224</v>
       </c>
       <c r="K11" t="n">
-        <v>1.4546</v>
+        <v>1.4479</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M11" t="n">
-        <v>0.9233</v>
+        <v>0.9495</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3129</v>
+        <v>0.3294</v>
       </c>
       <c r="O11" t="n">
-        <v>0.6105</v>
+        <v>0.6201</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6732</v>
+        <v>0.2418</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1179</v>
+        <v>-0.0468</v>
       </c>
       <c r="U11" t="n">
-        <v>0.7912</v>
+        <v>0.2886</v>
       </c>
       <c r="V11" t="n">
-        <v>-4.0492</v>
+        <v>-4.0424</v>
       </c>
       <c r="W11" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X11" t="n">
-        <v>-4.3707</v>
+        <v>-4.3579</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.9588</v>
+        <v>-2.872</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.5019</v>
+        <v>-3.4916</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5432</v>
+        <v>0.6196</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.0538</v>
+        <v>-4.0732</v>
       </c>
       <c r="H12" t="n">
-        <v>1.0188</v>
+        <v>1.0114</v>
       </c>
       <c r="I12" t="n">
-        <v>-5.0726</v>
+        <v>-5.0846</v>
       </c>
       <c r="J12" t="n">
-        <v>-4.4149</v>
+        <v>-4.4635</v>
       </c>
       <c r="K12" t="n">
-        <v>1.0523</v>
+        <v>1.0267</v>
       </c>
       <c r="L12" t="n">
-        <v>-5.4672</v>
+        <v>-5.4903</v>
       </c>
       <c r="M12" t="n">
-        <v>0.3611</v>
+        <v>0.3903</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.0335</v>
+        <v>-0.0154</v>
       </c>
       <c r="O12" t="n">
-        <v>0.3946</v>
+        <v>0.4057</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R12" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S12" t="n">
-        <v>1.524</v>
+        <v>0.6352</v>
       </c>
       <c r="T12" t="n">
-        <v>1.4911</v>
+        <v>0.5732</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0329</v>
+        <v>0.062</v>
       </c>
       <c r="V12" t="n">
-        <v>1.4783</v>
+        <v>1.4764</v>
       </c>
       <c r="W12" t="n">
-        <v>3.8243</v>
+        <v>3.8132</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="13">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>12.2606</v>
+        <v>13.3163</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.547500000000001</v>
+        <v>-0.8416000000000006</v>
       </c>
       <c r="F13" t="n">
-        <v>13.8082</v>
+        <v>14.1578</v>
       </c>
       <c r="G13" t="n">
-        <v>10.3817</v>
+        <v>10.4097</v>
       </c>
       <c r="H13" t="n">
-        <v>10.3816</v>
+        <v>10.4099</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>8.881784197001252e-16</v>
       </c>
       <c r="J13" t="n">
-        <v>2.800199999999999</v>
+        <v>2.5665</v>
       </c>
       <c r="K13" t="n">
-        <v>9.6915</v>
+        <v>9.557</v>
       </c>
       <c r="L13" t="n">
-        <v>-6.891</v>
+        <v>-6.9908</v>
       </c>
       <c r="M13" t="n">
-        <v>7.581200000000001</v>
+        <v>7.843400000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>0.6901</v>
+        <v>0.8528</v>
       </c>
       <c r="O13" t="n">
-        <v>6.8913</v>
+        <v>6.9908</v>
       </c>
       <c r="P13" t="n">
         <v>-3.33066907387547e-16</v>
       </c>
       <c r="Q13" t="n">
-        <v>-17.0124</v>
+        <v>-17.0724</v>
       </c>
       <c r="R13" t="n">
-        <v>17.0126</v>
+        <v>17.0724</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3003</v>
+        <v>2.347</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7413000000000001</v>
+        <v>1.8082</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5593</v>
+        <v>0.5386</v>
       </c>
       <c r="V13" t="n">
-        <v>0.5788000000000002</v>
+        <v>0.5597000000000003</v>
       </c>
       <c r="W13" t="n">
-        <v>11.9233</v>
+        <v>11.8562</v>
       </c>
       <c r="X13" t="n">
-        <v>-11.3447</v>
+        <v>-11.2966</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. DE SOUSA</t>
+          <t>G. CORBALAN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.1598</v>
+        <v>5.0006</v>
       </c>
       <c r="E14" t="n">
-        <v>4.483</v>
+        <v>5.327</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3232</v>
+        <v>-0.3264</v>
       </c>
       <c r="G14" t="n">
-        <v>3.252</v>
+        <v>1.1284</v>
       </c>
       <c r="H14" t="n">
-        <v>1.4313</v>
+        <v>2.2352</v>
       </c>
       <c r="I14" t="n">
-        <v>1.8206</v>
+        <v>-1.1068</v>
       </c>
       <c r="J14" t="n">
-        <v>2.4004</v>
+        <v>1.9001</v>
       </c>
       <c r="K14" t="n">
-        <v>2.2512</v>
+        <v>3.0402</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1493</v>
+        <v>-1.1401</v>
       </c>
       <c r="M14" t="n">
-        <v>0.8515</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.8198</v>
+        <v>-0.805</v>
       </c>
       <c r="O14" t="n">
-        <v>1.6714</v>
+        <v>0.0333</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2268</v>
+        <v>1.3658</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R14" t="n">
-        <v>0.6805</v>
+        <v>1.8211</v>
       </c>
       <c r="S14" t="n">
-        <v>1.2273</v>
+        <v>-0.2173</v>
       </c>
       <c r="T14" t="n">
-        <v>1.1221</v>
+        <v>-0.0887</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1052</v>
+        <v>-0.1286</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.5463</v>
+        <v>2.7237</v>
       </c>
       <c r="W14" t="n">
-        <v>1.4141</v>
+        <v>3.9709</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.9604</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. CORBALAN</t>
+          <t>S. DE SOUSA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.1536</v>
+        <v>3.6522</v>
       </c>
       <c r="E15" t="n">
-        <v>4.6735</v>
+        <v>3.8757</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5199</v>
+        <v>-0.2235</v>
       </c>
       <c r="G15" t="n">
-        <v>1.1421</v>
+        <v>3.2654</v>
       </c>
       <c r="H15" t="n">
-        <v>2.2483</v>
+        <v>1.4358</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.1062</v>
+        <v>1.8296</v>
       </c>
       <c r="J15" t="n">
-        <v>1.9406</v>
+        <v>2.3897</v>
       </c>
       <c r="K15" t="n">
-        <v>3.0682</v>
+        <v>2.2408</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.1276</v>
+        <v>0.1489</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.7984</v>
+        <v>0.8757</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8198</v>
+        <v>-0.805</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0214</v>
+        <v>1.6807</v>
       </c>
       <c r="P15" t="n">
-        <v>1.361</v>
+        <v>0.2276</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8147</v>
+        <v>0.6829</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0812</v>
+        <v>0.7039</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7984</v>
+        <v>0.5362</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2828</v>
+        <v>0.1677</v>
       </c>
       <c r="V15" t="n">
-        <v>2.7317</v>
+        <v>-0.5447</v>
       </c>
       <c r="W15" t="n">
-        <v>3.9851</v>
+        <v>1.405</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2534</v>
+        <v>-1.9497</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. DIEZ</t>
+          <t>J. RUBIO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0422</v>
+        <v>0.8796</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.7332</v>
+        <v>-0.5793</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7754</v>
+        <v>1.4589</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1075</v>
+        <v>-0.8844</v>
       </c>
       <c r="H16" t="n">
-        <v>-3.251</v>
+        <v>-0.5865</v>
       </c>
       <c r="I16" t="n">
-        <v>3.3585</v>
+        <v>-0.2979</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6681</v>
+        <v>-1.3152</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.0776</v>
+        <v>0.1896</v>
       </c>
       <c r="L16" t="n">
-        <v>1.7458</v>
+        <v>-1.5048</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.5606</v>
+        <v>0.4308</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.1734</v>
+        <v>-0.7761</v>
       </c>
       <c r="O16" t="n">
-        <v>1.6127</v>
+        <v>1.2069</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.2268</v>
+        <v>1.1382</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.722</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.4952</v>
+        <v>1.1382</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6152</v>
+        <v>0.4681</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7743</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1591</v>
+        <v>-0.11</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5463</v>
+        <v>0.1578</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5463</v>
+        <v>0.1578</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. SAMUELS JR</t>
+          <t>D. DIEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0016</v>
+        <v>0.7543</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.6737</v>
+        <v>-1.247</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6754</v>
+        <v>2.0013</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.161</v>
+        <v>0.1029</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1774</v>
+        <v>-3.2485</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9835</v>
+        <v>3.3513</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.1615</v>
+        <v>0.6337</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.4125</v>
+        <v>-1.0934</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.749</v>
+        <v>1.7271</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0005999999999999999</v>
+        <v>-0.5309</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2351</v>
+        <v>-2.1551</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2345</v>
+        <v>1.6242</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1342</v>
+        <v>-2.7316</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9073</v>
+        <v>2.5039</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6863</v>
+        <v>0.3344</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5293</v>
+        <v>0.3061</v>
       </c>
       <c r="U17" t="n">
-        <v>0.157</v>
+        <v>0.0283</v>
       </c>
       <c r="V17" t="n">
-        <v>1.7032</v>
+        <v>0.5447</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0927</v>
+        <v>0.5447</v>
       </c>
       <c r="X17" t="n">
-        <v>0.6105</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. RUBIO</t>
+          <t>J. SAMUELS JR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2763</v>
+        <v>0.4476</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6902</v>
+        <v>-1.284</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9665</v>
+        <v>1.7316</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.8961</v>
+        <v>-1.1592</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5976</v>
+        <v>-0.1808</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2985</v>
+        <v>-0.9785</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.3076</v>
+        <v>-1.1768</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1905</v>
+        <v>-0.4244</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.4981</v>
+        <v>-0.7524</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4115</v>
+        <v>0.0176</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.788</v>
+        <v>0.2437</v>
       </c>
       <c r="O18" t="n">
-        <v>1.1995</v>
+        <v>-0.226</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1342</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1342</v>
+        <v>0.9105</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1225</v>
+        <v>0.1288</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4567</v>
+        <v>-0.0585</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5792</v>
+        <v>0.1873</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1607</v>
+        <v>1.7057</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1607</v>
+        <v>1.0895</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.6162</v>
       </c>
     </row>
     <row r="19">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3682</v>
+        <v>-0.3979</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6346</v>
+        <v>-1.6669</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2664</v>
+        <v>1.269</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.6301</v>
+        <v>-1.6302</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.6275</v>
+        <v>-1.6366</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0026</v>
+        <v>0.0064</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.293</v>
+        <v>-0.3122</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.3676</v>
+        <v>-0.3867</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.3371</v>
+        <v>-1.318</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.2599</v>
+        <v>-1.2499</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0772</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R19" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1237</v>
+        <v>-0.1546</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3266</v>
+        <v>-0.3256</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2029</v>
+        <v>0.171</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="20">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.005</v>
+        <v>-1.3893</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0451</v>
+        <v>-0.9019</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0501</v>
+        <v>-0.4874</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1259</v>
+        <v>0.1389</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3407</v>
+        <v>-0.3336</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4665</v>
+        <v>0.4725</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6051</v>
+        <v>-0.609</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0693</v>
+        <v>0.0689</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6744</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>0.731</v>
+        <v>0.7479</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4099</v>
+        <v>-0.4025</v>
       </c>
       <c r="O20" t="n">
-        <v>1.1409</v>
+        <v>1.1504</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6028</v>
+        <v>0.1939</v>
       </c>
       <c r="T20" t="n">
-        <v>1.1039</v>
+        <v>0.1623</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5012</v>
+        <v>0.0316</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.9604</v>
+        <v>-1.9497</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.9604</v>
+        <v>-1.9497</v>
       </c>
     </row>
     <row r="21">
@@ -2047,40 +2047,40 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7618</v>
+        <v>-1.612</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5278</v>
+        <v>-0.4157</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.234</v>
+        <v>-1.1964</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3241</v>
+        <v>-0.3263</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6782</v>
+        <v>0.6778</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.0023</v>
+        <v>-1.0041</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.2495</v>
+        <v>-0.2553</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5368000000000001</v>
+        <v>0.5343</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0745</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>0.1414</v>
+        <v>0.1435</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2159</v>
+        <v>-0.2144</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -2092,22 +2092,22 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3451</v>
+        <v>-0.1963</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2782</v>
+        <v>-0.1604</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0668</v>
+        <v>-0.0359</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7923</v>
+        <v>-2.8228</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.9618</v>
+        <v>-1.9784</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8306</v>
+        <v>-0.8444</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5068</v>
+        <v>0.5083</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.2871</v>
+        <v>-1.2867</v>
       </c>
       <c r="I22" t="n">
-        <v>1.7939</v>
+        <v>1.795</v>
       </c>
       <c r="J22" t="n">
-        <v>1.0022</v>
+        <v>0.995</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.7517</v>
+        <v>-0.7552</v>
       </c>
       <c r="L22" t="n">
-        <v>1.7539</v>
+        <v>1.7501</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.4954</v>
+        <v>-0.4866</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5354</v>
+        <v>-0.5315</v>
       </c>
       <c r="O22" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5259</v>
+        <v>-0.5587</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6956</v>
+        <v>-0.697</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1697</v>
+        <v>0.1383</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="23">
@@ -2203,40 +2203,40 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.926</v>
+        <v>-2.8777</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.0845</v>
+        <v>-0.9836</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.8415</v>
+        <v>-1.8942</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.8661</v>
+        <v>-1.8731</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.528</v>
+        <v>-0.5339</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.3381</v>
+        <v>-1.3392</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.2135</v>
+        <v>-1.2285</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.4644</v>
+        <v>-0.4761</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.6526</v>
+        <v>-0.6446</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0636</v>
+        <v>-0.0578</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.5891</v>
+        <v>-0.5868</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -2248,28 +2248,28 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5135999999999999</v>
+        <v>-0.4599</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4174</v>
+        <v>-0.2998</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.09619999999999999</v>
+        <v>-0.1601</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W23" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>L. MEINDL</t>
+          <t>J. JACKSON</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.8965</v>
+        <v>-5.7343</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.4317</v>
+        <v>-7.2906</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5352</v>
+        <v>1.5563</v>
       </c>
       <c r="G24" t="n">
-        <v>-8.8088</v>
+        <v>-0.8591</v>
       </c>
       <c r="H24" t="n">
-        <v>-5.2263</v>
+        <v>-1.7195</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.5825</v>
+        <v>0.8604000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>-7.5336</v>
+        <v>-1.2903</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.7138</v>
+        <v>-0.0527</v>
       </c>
       <c r="L24" t="n">
-        <v>-3.8198</v>
+        <v>-1.2376</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.2752</v>
+        <v>0.4311</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.5125</v>
+        <v>-1.6668</v>
       </c>
       <c r="O24" t="n">
-        <v>0.2373</v>
+        <v>2.098</v>
       </c>
       <c r="P24" t="n">
-        <v>1.5878</v>
+        <v>-3.4145</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.361</v>
+        <v>-5.9184</v>
       </c>
       <c r="R24" t="n">
-        <v>2.9488</v>
+        <v>2.5039</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3826</v>
+        <v>0.1021</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8831</v>
+        <v>-0.0819</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5004999999999999</v>
+        <v>0.184</v>
       </c>
       <c r="V24" t="n">
-        <v>0.7071</v>
+        <v>-1.5628</v>
       </c>
       <c r="W24" t="n">
-        <v>2.3461</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.639</v>
+        <v>-1.5628</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J. JACKSON</t>
+          <t>L. MEINDL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.1444</v>
+        <v>-6.5918</v>
       </c>
       <c r="E25" t="n">
-        <v>-8.272500000000001</v>
+        <v>-7.0131</v>
       </c>
       <c r="F25" t="n">
-        <v>1.128</v>
+        <v>0.4213</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.8297</v>
+        <v>-8.821300000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.7039</v>
+        <v>-5.2326</v>
       </c>
       <c r="I25" t="n">
-        <v>0.8742</v>
+        <v>-3.5888</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.2286</v>
+        <v>-7.5746</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.0182</v>
+        <v>-3.7381</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.2104</v>
+        <v>-3.8365</v>
       </c>
       <c r="M25" t="n">
-        <v>0.3989</v>
+        <v>-1.2467</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.6857</v>
+        <v>-1.4945</v>
       </c>
       <c r="O25" t="n">
-        <v>2.0846</v>
+        <v>0.2477</v>
       </c>
       <c r="P25" t="n">
-        <v>-3.4025</v>
+        <v>1.5934</v>
       </c>
       <c r="Q25" t="n">
-        <v>-5.8976</v>
+        <v>-1.3658</v>
       </c>
       <c r="R25" t="n">
-        <v>2.4952</v>
+        <v>2.9592</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.3374</v>
+        <v>-0.0664</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.1462</v>
+        <v>-0.4094</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1912</v>
+        <v>0.343</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.5748</v>
+        <v>0.7025</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.3367</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.5748</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-12.2607</v>
+        <v>-10.6915</v>
       </c>
       <c r="E26" t="n">
-        <v>-13.8084</v>
+        <v>-14.1578</v>
       </c>
       <c r="F26" t="n">
-        <v>1.5476</v>
+        <v>3.4661</v>
       </c>
       <c r="G26" t="n">
-        <v>-10.3816</v>
+        <v>-10.4097</v>
       </c>
       <c r="H26" t="n">
-        <v>-10.3817</v>
+        <v>-10.4099</v>
       </c>
       <c r="I26" t="n">
-        <v>3.33066907387547e-16</v>
+        <v>-9.999999999976694e-05</v>
       </c>
       <c r="J26" t="n">
-        <v>-7.581099999999999</v>
+        <v>-7.8434</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.6897999999999997</v>
+        <v>-0.8528000000000007</v>
       </c>
       <c r="L26" t="n">
-        <v>-6.8911</v>
+        <v>-6.990699999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>-2.8003</v>
+        <v>-2.5664</v>
       </c>
       <c r="N26" t="n">
-        <v>-9.6915</v>
+        <v>-9.557</v>
       </c>
       <c r="O26" t="n">
-        <v>6.8911</v>
+        <v>6.9908</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>-2.220446049250313e-16</v>
       </c>
       <c r="Q26" t="n">
-        <v>-17.0125</v>
+        <v>-17.0725</v>
       </c>
       <c r="R26" t="n">
-        <v>17.0126</v>
+        <v>17.0724</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.3004</v>
+        <v>0.2779999999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.5592000000000001</v>
+        <v>-0.5386000000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.7412000000000003</v>
+        <v>0.8166</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.5784999999999992</v>
+        <v>-0.5595000000000002</v>
       </c>
       <c r="W26" t="n">
-        <v>11.3447</v>
+        <v>11.2965</v>
       </c>
       <c r="X26" t="n">
-        <v>-11.9233</v>
+        <v>-11.8561</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104475_W2.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104475_W2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104475_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104475_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104475_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104475_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104475_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104475_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104475_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104475_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104475_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-4.3579</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104475_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104475_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-11.2966</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104475_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.9497</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104475_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104475_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104475_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0.6162</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104475_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104475_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.9497</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104475_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104475_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104475_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104475_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.5628</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104475_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104475_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-11.8561</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
